--- a/幻想少女公会招募图鉴.xlsx
+++ b/幻想少女公会招募图鉴.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$134</definedName>
     <definedName name="_xlnm.Criteria" localSheetId="0">Sheet1!$C$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="168">
   <si>
     <t>位阶</t>
   </si>
@@ -177,6 +177,9 @@
     <t>淘气恶魔</t>
   </si>
   <si>
+    <t>无尽领主</t>
+  </si>
+  <si>
     <t>无瑕贤者</t>
   </si>
   <si>
@@ -204,12 +207,6 @@
     <t>亡灵</t>
   </si>
   <si>
-    <t>无尽领主</t>
-  </si>
-  <si>
-    <t>许愿灯灵</t>
-  </si>
-  <si>
     <t>史诗</t>
   </si>
   <si>
@@ -252,12 +249,18 @@
     <t>荒野兽王</t>
   </si>
   <si>
+    <t>黄沙使者</t>
+  </si>
+  <si>
     <t>魂能法师</t>
   </si>
   <si>
     <t>火焰女妖</t>
   </si>
   <si>
+    <t>荆棘射手</t>
+  </si>
+  <si>
     <t>荆棘树妖</t>
   </si>
   <si>
@@ -282,6 +285,9 @@
     <t>狼灵射手</t>
   </si>
   <si>
+    <t>流沙刺客</t>
+  </si>
+  <si>
     <t>流水法师</t>
   </si>
   <si>
@@ -324,6 +330,9 @@
     <t>水族统领</t>
   </si>
   <si>
+    <t>蝎尾刺客</t>
+  </si>
+  <si>
     <t>星界守卫</t>
   </si>
   <si>
@@ -355,18 +364,6 @@
   </si>
   <si>
     <t>植物学者</t>
-  </si>
-  <si>
-    <t>蝎尾刺客</t>
-  </si>
-  <si>
-    <t>荆棘射手</t>
-  </si>
-  <si>
-    <t>流沙刺客</t>
-  </si>
-  <si>
-    <t>黄沙使者</t>
   </si>
   <si>
     <t>稀有</t>
@@ -1595,7 +1592,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr defaultColWidth="9.77777777777778" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="7.43518518518519" customWidth="1"/>
@@ -2005,23 +2002,23 @@
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>14</v>
+      <c r="C21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2032,16 +2029,16 @@
         <v>49</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2049,79 +2046,79 @@
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>11</v>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>20</v>
+      <c r="C25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>38</v>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2135,70 +2132,70 @@
         <v>13</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="5" t="s">
+    <row r="29" spans="1:6">
+      <c r="A29" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>27</v>
+      <c r="F29" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>18</v>
@@ -2206,187 +2203,187 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B31" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>18</v>
+      <c r="C31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>42</v>
+      <c r="C32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="C34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>38</v>
+      <c r="F34" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="3" t="s">
+      <c r="C35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>20</v>
+      <c r="F35" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B39" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F39" s="2" t="s">
+      <c r="C39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>70</v>
@@ -2398,15 +2395,15 @@
         <v>9</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>71</v>
@@ -2418,35 +2415,35 @@
         <v>9</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F41" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="5" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>73</v>
@@ -2466,7 +2463,7 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>74</v>
@@ -2485,77 +2482,77 @@
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45" s="2" t="s">
+      <c r="A45" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="2" t="s">
+      <c r="C45" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F45" s="2" t="s">
-        <v>38</v>
+      <c r="F45" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B46" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="3" t="s">
+      <c r="C46" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B47" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>18</v>
+      <c r="C47" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>17</v>
@@ -2566,47 +2563,47 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B50" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F50" s="3" t="s">
+      <c r="C50" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>81</v>
@@ -2615,10 +2612,10 @@
         <v>13</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>20</v>
@@ -2626,187 +2623,187 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F52" s="2" t="s">
+      <c r="C52" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>18</v>
+      <c r="E54" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B57" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>20</v>
+      <c r="C57" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>32</v>
+        <v>9</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B59" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>38</v>
+      <c r="C59" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>91</v>
@@ -2818,267 +2815,267 @@
         <v>9</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B65" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>20</v>
+      <c r="C65" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B66" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>14</v>
+      <c r="C66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>50</v>
+      <c r="C67" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B68" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F68" s="2" t="s">
+      <c r="C68" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F69" s="5" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B72" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>56</v>
+      <c r="C72" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>42</v>
+        <v>17</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B73" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E73" s="3" t="s">
+      <c r="C73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="F73" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>27</v>
@@ -3086,159 +3083,159 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>26</v>
+        <v>57</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B76" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>20</v>
+      <c r="C76" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C77" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E77" s="2" t="s">
+      <c r="D78" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F77" s="2" t="s">
+      <c r="F80" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
-      <c r="A78" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="5" t="s">
+    <row r="81" spans="1:6">
+      <c r="A81" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E80" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>27</v>
+      <c r="E81" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>18</v>
@@ -3246,19 +3243,19 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>18</v>
@@ -3266,73 +3263,73 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>9</v>
@@ -3346,7 +3343,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>119</v>
@@ -3358,18 +3355,18 @@
         <v>9</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>20</v>
+        <v>120</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>13</v>
@@ -3381,12 +3378,12 @@
         <v>32</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>121</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>122</v>
@@ -3398,7 +3395,7 @@
         <v>9</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>20</v>
@@ -3406,7 +3403,7 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>123</v>
@@ -3421,18 +3418,18 @@
         <v>17</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>9</v>
@@ -3446,7 +3443,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>125</v>
@@ -3458,35 +3455,35 @@
         <v>9</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>127</v>
@@ -3498,21 +3495,21 @@
         <v>9</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>9</v>
@@ -3526,19 +3523,19 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>20</v>
@@ -3546,7 +3543,7 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>130</v>
@@ -3555,70 +3552,70 @@
         <v>16</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>38</v>
@@ -3626,7 +3623,7 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>134</v>
@@ -3638,15 +3635,15 @@
         <v>9</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>135</v>
@@ -3658,67 +3655,67 @@
         <v>9</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>38</v>
@@ -3726,19 +3723,19 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>38</v>
@@ -3746,53 +3743,53 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>9</v>
@@ -3806,7 +3803,7 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>143</v>
@@ -3818,44 +3815,44 @@
         <v>9</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>29</v>
@@ -3866,7 +3863,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>146</v>
@@ -3875,58 +3872,58 @@
         <v>13</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>29</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2" t="s">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>29</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B116" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B116" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C116" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E116" s="2" t="s">
+      <c r="C116" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F116" s="2" t="s">
+      <c r="F116" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="117" spans="1:6">
-      <c r="A117" s="2" t="s">
-        <v>148</v>
+      <c r="A117" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>150</v>
@@ -3938,46 +3935,46 @@
         <v>9</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F117" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F118" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
-      <c r="A118" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
     <row r="119" spans="1:6">
-      <c r="A119" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B119" s="2" t="s">
+      <c r="A119" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B119" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="C119" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E119" s="2" t="s">
+      <c r="C119" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" s="6" t="s">
         <v>22</v>
       </c>
       <c r="F119" s="2" t="s">
@@ -3985,28 +3982,28 @@
       </c>
     </row>
     <row r="120" spans="1:6">
-      <c r="A120" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="B120" s="6" t="s">
+      <c r="A120" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B120" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C120" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E120" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>20</v>
+      <c r="C120" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>154</v>
@@ -4025,239 +4022,239 @@
       </c>
     </row>
     <row r="122" spans="1:6">
-      <c r="A122" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B122" s="3" t="s">
+      <c r="A122" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C122" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F122" s="3" t="s">
-        <v>27</v>
+      <c r="C122" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B123" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B123" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C123" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E123" s="2" t="s">
+      <c r="C123" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F123" s="2" t="s">
+      <c r="F123" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B124" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C124" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F124" s="3" t="s">
-        <v>20</v>
+      <c r="C124" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B125" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B125" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E125" s="2" t="s">
+      <c r="C125" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F125" s="2" t="s">
+      <c r="F125" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B126" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C126" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F126" s="3" t="s">
+      <c r="C126" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F126" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="128" spans="1:6">
-      <c r="A128" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B128" s="2" t="s">
+      <c r="A128" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B128" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C128" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C130" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D128" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D129" s="6" t="s">
+      <c r="D130" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E129" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F129" s="6" t="s">
+      <c r="E130" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F130" s="7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
-      <c r="A130" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F130" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
     <row r="131" spans="1:6">
-      <c r="A131" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="B131" s="7" t="s">
+      <c r="A131" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C131" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D131" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E131" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F131" s="7" t="s">
+      <c r="C131" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F131" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="133" spans="1:6">
-      <c r="A133" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B133" s="2" t="s">
+      <c r="A133" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B133" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C133" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E133" s="2" t="s">
+      <c r="C133" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E133" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F133" s="2" t="s">
@@ -4265,57 +4262,37 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="A134" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B134" s="3" t="s">
+      <c r="A134" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B134" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="C134" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E134" s="3" t="s">
+      <c r="C134" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F134" s="2" t="s">
+      <c r="F134" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
-      <c r="A135" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C135" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F135" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F135" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:F135">
-      <sortCondition ref="A2:A129" customList="橙色,紫色,蓝色,绿色"/>
-      <sortCondition ref="B2:B129"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F134" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:F134">
+      <sortCondition ref="A2:A134" customList="传说,史诗,稀有,普通"/>
+      <sortCondition ref="B2:B134"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <sortState ref="A2:F135">
     <sortCondition ref="A2:A135" customList="橙色,紫色,蓝色,绿色"/>
   </sortState>
-  <conditionalFormatting sqref="A2:F230">
+  <conditionalFormatting sqref="A2:F229">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$A2="传说"</formula>
     </cfRule>

--- a/幻想少女公会招募图鉴.xlsx
+++ b/幻想少女公会招募图鉴.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="167">
   <si>
     <t>位阶</t>
   </si>
@@ -163,9 +163,6 @@
   </si>
   <si>
     <t>圣剑之灵</t>
-  </si>
-  <si>
-    <t>器炅</t>
   </si>
   <si>
     <t>史莱姆王</t>
@@ -1932,7 +1929,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>32</v>
@@ -1946,7 +1943,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>16</v>
@@ -1966,7 +1963,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>16</v>
@@ -1986,7 +1983,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>13</v>
@@ -2006,7 +2003,7 @@
         <v>6</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>13</v>
@@ -2026,7 +2023,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>36</v>
@@ -2046,7 +2043,7 @@
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>16</v>
@@ -2058,7 +2055,7 @@
         <v>29</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2066,7 +2063,7 @@
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>8</v>
@@ -2078,7 +2075,7 @@
         <v>32</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2086,7 +2083,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>13</v>
@@ -2106,7 +2103,7 @@
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>8</v>
@@ -2126,7 +2123,7 @@
         <v>6</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>13</v>
@@ -2146,13 +2143,13 @@
         <v>6</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>29</v>
@@ -2163,10 +2160,10 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>16</v>
@@ -2183,10 +2180,10 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>8</v>
@@ -2203,10 +2200,10 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>13</v>
@@ -2223,10 +2220,10 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>16</v>
@@ -2243,10 +2240,10 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>8</v>
@@ -2263,10 +2260,10 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>13</v>
@@ -2283,10 +2280,10 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>16</v>
@@ -2303,10 +2300,10 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>36</v>
@@ -2323,10 +2320,10 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>16</v>
@@ -2343,10 +2340,10 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>8</v>
@@ -2363,10 +2360,10 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>13</v>
@@ -2383,10 +2380,10 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>13</v>
@@ -2403,10 +2400,10 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>13</v>
@@ -2423,10 +2420,10 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>16</v>
@@ -2443,10 +2440,10 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>16</v>
@@ -2463,10 +2460,10 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>13</v>
@@ -2483,10 +2480,10 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>8</v>
@@ -2503,10 +2500,10 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>16</v>
@@ -2523,10 +2520,10 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>13</v>
@@ -2543,10 +2540,10 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>36</v>
@@ -2563,10 +2560,10 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>8</v>
@@ -2583,10 +2580,10 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>16</v>
@@ -2603,10 +2600,10 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>13</v>
@@ -2623,10 +2620,10 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>13</v>
@@ -2643,10 +2640,10 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>8</v>
@@ -2663,10 +2660,10 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>8</v>
@@ -2683,10 +2680,10 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>16</v>
@@ -2703,10 +2700,10 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>8</v>
@@ -2723,10 +2720,10 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>36</v>
@@ -2743,10 +2740,10 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>36</v>
@@ -2763,10 +2760,10 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>13</v>
@@ -2783,10 +2780,10 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>13</v>
@@ -2803,10 +2800,10 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>8</v>
@@ -2823,10 +2820,10 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>16</v>
@@ -2843,10 +2840,10 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>8</v>
@@ -2863,10 +2860,10 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>8</v>
@@ -2883,10 +2880,10 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>13</v>
@@ -2903,10 +2900,10 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>16</v>
@@ -2923,10 +2920,10 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>13</v>
@@ -2943,10 +2940,10 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>13</v>
@@ -2963,10 +2960,10 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>13</v>
@@ -2983,10 +2980,10 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>13</v>
@@ -2998,15 +2995,15 @@
         <v>29</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>16</v>
@@ -3023,10 +3020,10 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>13</v>
@@ -3043,10 +3040,10 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>8</v>
@@ -3063,10 +3060,10 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>8</v>
@@ -3083,16 +3080,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>29</v>
@@ -3103,10 +3100,10 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>13</v>
@@ -3123,10 +3120,10 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>16</v>
@@ -3143,10 +3140,10 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>36</v>
@@ -3163,10 +3160,10 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>36</v>
@@ -3183,10 +3180,10 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>36</v>
@@ -3203,10 +3200,10 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>36</v>
@@ -3223,10 +3220,10 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>8</v>
@@ -3243,10 +3240,10 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>13</v>
@@ -3263,10 +3260,10 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>8</v>
@@ -3283,10 +3280,10 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>13</v>
@@ -3303,10 +3300,10 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>16</v>
@@ -3323,10 +3320,10 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>13</v>
@@ -3343,10 +3340,10 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>13</v>
@@ -3358,15 +3355,15 @@
         <v>32</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>13</v>
@@ -3383,10 +3380,10 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>13</v>
@@ -3403,10 +3400,10 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>13</v>
@@ -3423,10 +3420,10 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>8</v>
@@ -3443,10 +3440,10 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>8</v>
@@ -3463,10 +3460,10 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>13</v>
@@ -3483,10 +3480,10 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>13</v>
@@ -3503,10 +3500,10 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>8</v>
@@ -3523,10 +3520,10 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>16</v>
@@ -3543,16 +3540,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>29</v>
@@ -3563,10 +3560,10 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>13</v>
@@ -3583,10 +3580,10 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>36</v>
@@ -3603,10 +3600,10 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>13</v>
@@ -3623,10 +3620,10 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>13</v>
@@ -3643,10 +3640,10 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>13</v>
@@ -3663,10 +3660,10 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>16</v>
@@ -3683,10 +3680,10 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>36</v>
@@ -3703,10 +3700,10 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>16</v>
@@ -3723,10 +3720,10 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>8</v>
@@ -3743,10 +3740,10 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>16</v>
@@ -3763,10 +3760,10 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>36</v>
@@ -3783,10 +3780,10 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>13</v>
@@ -3803,10 +3800,10 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>13</v>
@@ -3823,16 +3820,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>29</v>
@@ -3843,16 +3840,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>29</v>
@@ -3863,10 +3860,10 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>13</v>
@@ -3883,10 +3880,10 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>8</v>
@@ -3903,10 +3900,10 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>13</v>
@@ -3923,10 +3920,10 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>13</v>
@@ -3943,10 +3940,10 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>8</v>
@@ -3963,10 +3960,10 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>13</v>
@@ -3983,10 +3980,10 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>13</v>
@@ -4003,10 +4000,10 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>13</v>
@@ -4023,10 +4020,10 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>36</v>
@@ -4043,10 +4040,10 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>13</v>
@@ -4063,10 +4060,10 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>8</v>
@@ -4083,10 +4080,10 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>13</v>
@@ -4103,10 +4100,10 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>16</v>
@@ -4123,10 +4120,10 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>36</v>
@@ -4143,10 +4140,10 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>13</v>
@@ -4163,10 +4160,10 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>16</v>
@@ -4183,10 +4180,10 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>36</v>
@@ -4203,10 +4200,10 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>8</v>
@@ -4223,10 +4220,10 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>36</v>
@@ -4243,10 +4240,10 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>13</v>
@@ -4263,10 +4260,10 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>13</v>
@@ -4283,7 +4280,7 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F134" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:F134">
+    <sortState ref="A1:F134">
       <sortCondition ref="A2:A134" customList="传说,史诗,稀有,普通"/>
       <sortCondition ref="B2:B134"/>
     </sortState>

--- a/幻想少女公会招募图鉴.xlsx
+++ b/幻想少女公会招募图鉴.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="166">
   <si>
     <t>位阶</t>
   </si>
@@ -388,9 +388,6 @@
   </si>
   <si>
     <t>荒漢守卫</t>
-  </si>
-  <si>
-    <t>沙漢</t>
   </si>
   <si>
     <t>疾行闪光</t>
@@ -3355,7 +3352,7 @@
         <v>32</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3363,7 +3360,7 @@
         <v>110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>13</v>
@@ -3383,7 +3380,7 @@
         <v>110</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>13</v>
@@ -3403,7 +3400,7 @@
         <v>110</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>13</v>
@@ -3423,7 +3420,7 @@
         <v>110</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>8</v>
@@ -3443,7 +3440,7 @@
         <v>110</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>8</v>
@@ -3463,7 +3460,7 @@
         <v>110</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>13</v>
@@ -3483,7 +3480,7 @@
         <v>110</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>13</v>
@@ -3503,7 +3500,7 @@
         <v>110</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>8</v>
@@ -3523,7 +3520,7 @@
         <v>110</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>16</v>
@@ -3543,7 +3540,7 @@
         <v>110</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>16</v>
@@ -3563,7 +3560,7 @@
         <v>110</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>13</v>
@@ -3583,7 +3580,7 @@
         <v>110</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>36</v>
@@ -3603,7 +3600,7 @@
         <v>110</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>13</v>
@@ -3623,7 +3620,7 @@
         <v>110</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>13</v>
@@ -3643,7 +3640,7 @@
         <v>110</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>13</v>
@@ -3663,7 +3660,7 @@
         <v>110</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>16</v>
@@ -3683,7 +3680,7 @@
         <v>110</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>36</v>
@@ -3703,7 +3700,7 @@
         <v>110</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>16</v>
@@ -3723,7 +3720,7 @@
         <v>110</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>8</v>
@@ -3743,7 +3740,7 @@
         <v>110</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>16</v>
@@ -3763,7 +3760,7 @@
         <v>110</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>36</v>
@@ -3783,7 +3780,7 @@
         <v>110</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>13</v>
@@ -3803,7 +3800,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>13</v>
@@ -3823,7 +3820,7 @@
         <v>110</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>8</v>
@@ -3843,7 +3840,7 @@
         <v>110</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>13</v>
@@ -3863,7 +3860,7 @@
         <v>110</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>13</v>
@@ -3880,10 +3877,10 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>8</v>
@@ -3900,10 +3897,10 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>13</v>
@@ -3920,10 +3917,10 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>13</v>
@@ -3940,10 +3937,10 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>8</v>
@@ -3960,10 +3957,10 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>13</v>
@@ -3980,10 +3977,10 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>13</v>
@@ -4000,10 +3997,10 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>13</v>
@@ -4020,10 +4017,10 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>36</v>
@@ -4040,10 +4037,10 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>13</v>
@@ -4060,10 +4057,10 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>8</v>
@@ -4080,10 +4077,10 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>13</v>
@@ -4100,10 +4097,10 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>16</v>
@@ -4120,10 +4117,10 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>36</v>
@@ -4140,10 +4137,10 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>13</v>
@@ -4160,10 +4157,10 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>16</v>
@@ -4180,10 +4177,10 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>36</v>
@@ -4200,10 +4197,10 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>8</v>
@@ -4220,10 +4217,10 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>36</v>
@@ -4240,10 +4237,10 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>13</v>
@@ -4260,10 +4257,10 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>13</v>

--- a/幻想少女公会招募图鉴.xlsx
+++ b/幻想少女公会招募图鉴.xlsx
@@ -387,7 +387,7 @@
     <t>哥布林战士</t>
   </si>
   <si>
-    <t>荒漢守卫</t>
+    <t>荒漠守卫</t>
   </si>
   <si>
     <t>疾行闪光</t>
@@ -4277,7 +4277,7 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F134" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:F134">
+    <sortState ref="A2:F134">
       <sortCondition ref="A2:A134" customList="传说,史诗,稀有,普通"/>
       <sortCondition ref="B2:B134"/>
     </sortState>

--- a/幻想少女公会招募图鉴.xlsx
+++ b/幻想少女公会招募图鉴.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$134</definedName>
-    <definedName name="_xlnm.Criteria" localSheetId="0">Sheet1!$C$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$133</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="0">Sheet1!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="165">
   <si>
     <t>位阶</t>
   </si>
@@ -54,142 +54,139 @@
     <t>传说</t>
   </si>
   <si>
-    <t>冰蛛女王</t>
+    <t>辰龙</t>
+  </si>
+  <si>
+    <t>战士</t>
+  </si>
+  <si>
+    <t>生灵</t>
+  </si>
+  <si>
+    <t>水系</t>
+  </si>
+  <si>
+    <t>沙滩</t>
+  </si>
+  <si>
+    <t>大地魔女</t>
+  </si>
+  <si>
+    <t>法师</t>
+  </si>
+  <si>
+    <t>地系</t>
+  </si>
+  <si>
+    <t>山脉</t>
+  </si>
+  <si>
+    <t>地灵使者</t>
+  </si>
+  <si>
+    <t>平原</t>
+  </si>
+  <si>
+    <t>风行游侠</t>
   </si>
   <si>
     <t>射手</t>
   </si>
   <si>
-    <t>生灵</t>
-  </si>
-  <si>
-    <t>水系</t>
+    <t>风系</t>
+  </si>
+  <si>
+    <t>核心魔偶</t>
+  </si>
+  <si>
+    <t>器灵</t>
+  </si>
+  <si>
+    <t>荒漠舞姬</t>
+  </si>
+  <si>
+    <t>火系</t>
+  </si>
+  <si>
+    <t>沙漠</t>
+  </si>
+  <si>
+    <t>黄蜂魔女</t>
+  </si>
+  <si>
+    <t>暗系</t>
+  </si>
+  <si>
+    <t>黄金之女</t>
+  </si>
+  <si>
+    <t>魔灵</t>
+  </si>
+  <si>
+    <t>光系</t>
+  </si>
+  <si>
+    <t>巨灵之枪</t>
+  </si>
+  <si>
+    <t>军团统领</t>
+  </si>
+  <si>
+    <t>林中仙女</t>
+  </si>
+  <si>
+    <t>牧师</t>
+  </si>
+  <si>
+    <t>神灵</t>
+  </si>
+  <si>
+    <t>森林</t>
+  </si>
+  <si>
+    <t>蛮牛勇士</t>
+  </si>
+  <si>
+    <t>魔术大师</t>
+  </si>
+  <si>
+    <t>宁静水灵</t>
+  </si>
+  <si>
+    <t>海洋</t>
+  </si>
+  <si>
+    <t>圣剑之灵</t>
+  </si>
+  <si>
+    <t>史莱姆王</t>
+  </si>
+  <si>
+    <t>水晶菇娘</t>
+  </si>
+  <si>
+    <t>淘气恶魔</t>
+  </si>
+  <si>
+    <t>无尽领主</t>
+  </si>
+  <si>
+    <t>无瑕贤者</t>
+  </si>
+  <si>
+    <t>星界邪神</t>
+  </si>
+  <si>
+    <t>星界</t>
+  </si>
+  <si>
+    <t>星灵射手</t>
+  </si>
+  <si>
+    <t>雪人骑士</t>
   </si>
   <si>
     <t>雪原</t>
-  </si>
-  <si>
-    <t>辰龙</t>
-  </si>
-  <si>
-    <t>战士</t>
-  </si>
-  <si>
-    <t>沙滩</t>
-  </si>
-  <si>
-    <t>大地魔女</t>
-  </si>
-  <si>
-    <t>法师</t>
-  </si>
-  <si>
-    <t>地系</t>
-  </si>
-  <si>
-    <t>山脉</t>
-  </si>
-  <si>
-    <t>地灵使者</t>
-  </si>
-  <si>
-    <t>平原</t>
-  </si>
-  <si>
-    <t>风行游侠</t>
-  </si>
-  <si>
-    <t>风系</t>
-  </si>
-  <si>
-    <t>核心魔偶</t>
-  </si>
-  <si>
-    <t>器灵</t>
-  </si>
-  <si>
-    <t>荒漠舞姬</t>
-  </si>
-  <si>
-    <t>火系</t>
-  </si>
-  <si>
-    <t>沙漠</t>
-  </si>
-  <si>
-    <t>黄蜂魔女</t>
-  </si>
-  <si>
-    <t>暗系</t>
-  </si>
-  <si>
-    <t>黄金之女</t>
-  </si>
-  <si>
-    <t>魔灵</t>
-  </si>
-  <si>
-    <t>光系</t>
-  </si>
-  <si>
-    <t>巨灵之枪</t>
-  </si>
-  <si>
-    <t>军团统领</t>
-  </si>
-  <si>
-    <t>林中仙女</t>
-  </si>
-  <si>
-    <t>牧师</t>
-  </si>
-  <si>
-    <t>神灵</t>
-  </si>
-  <si>
-    <t>森林</t>
-  </si>
-  <si>
-    <t>蛮牛勇士</t>
-  </si>
-  <si>
-    <t>魔术大师</t>
-  </si>
-  <si>
-    <t>宁静水灵</t>
-  </si>
-  <si>
-    <t>海洋</t>
-  </si>
-  <si>
-    <t>圣剑之灵</t>
-  </si>
-  <si>
-    <t>史莱姆王</t>
-  </si>
-  <si>
-    <t>水晶菇娘</t>
-  </si>
-  <si>
-    <t>淘气恶魔</t>
-  </si>
-  <si>
-    <t>无尽领主</t>
-  </si>
-  <si>
-    <t>无瑕贤者</t>
-  </si>
-  <si>
-    <t>星界邪神</t>
-  </si>
-  <si>
-    <t>星界</t>
-  </si>
-  <si>
-    <t>星灵射手</t>
-  </si>
-  <si>
-    <t>雪人骑士</t>
   </si>
   <si>
     <t>鹰身公主</t>
@@ -1586,7 +1583,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F133"/>
   <sheetFormatPr defaultColWidth="9.77777777777778" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="7.43518518518519" customWidth="1"/>
@@ -1619,19 +1616,19 @@
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1639,20 +1636,20 @@
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1660,19 +1657,19 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1680,59 +1677,59 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="C6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>20</v>
+      <c r="E6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>18</v>
+      <c r="F7" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1740,39 +1737,39 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="C9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>20</v>
+      <c r="E9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1780,39 +1777,39 @@
         <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1820,59 +1817,59 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>38</v>
+      <c r="C13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="B14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>20</v>
+      <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1880,139 +1877,139 @@
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="2" t="s">
+      <c r="D18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="4" t="s">
+      <c r="C19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="2" t="s">
+      <c r="C20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>27</v>
+      <c r="C21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2020,19 +2017,19 @@
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2043,76 +2040,76 @@
         <v>49</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>11</v>
+      <c r="C25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>20</v>
+      <c r="C26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2123,707 +2120,707 @@
         <v>54</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>42</v>
+      <c r="D28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>18</v>
+      <c r="C30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>42</v>
+      <c r="D31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>38</v>
+      <c r="C33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="3" t="s">
+      <c r="D34" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="E34" s="2" t="s">
         <v>20</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E37" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>20</v>
+      <c r="C38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F40" s="3" t="s">
+      <c r="D41" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>27</v>
+      <c r="F42" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E43" s="2" t="s">
+      <c r="C43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>38</v>
+      <c r="E43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="A44" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>27</v>
+      <c r="D45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B46" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>38</v>
+      <c r="C46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>38</v>
+      <c r="C47" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>20</v>
+      <c r="C50" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B52" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="2" t="s">
+      <c r="D54" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>27</v>
+      <c r="E54" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" s="2" t="s">
+      <c r="C58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B59" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>9</v>
+      <c r="C59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>32</v>
+        <v>9</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>9</v>
@@ -2832,32 +2829,32 @@
         <v>10</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>93</v>
@@ -2866,18 +2863,18 @@
         <v>8</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>94</v>
@@ -2886,98 +2883,98 @@
         <v>13</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B66" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>27</v>
+      <c r="C66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B68" s="3" t="s">
+      <c r="A68" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B68" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>14</v>
+      <c r="C68" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B69" s="5" t="s">
+      <c r="A69" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C69" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>38</v>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>99</v>
@@ -2986,78 +2983,78 @@
         <v>13</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B71" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>38</v>
+      <c r="C71" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B72" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C72" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>18</v>
+      <c r="C72" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>103</v>
@@ -3066,158 +3063,158 @@
         <v>8</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>17</v>
+        <v>55</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B75" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>56</v>
+      <c r="C75" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>42</v>
+        <v>20</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B76" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B76" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>14</v>
+      <c r="D76" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C79" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F79" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>112</v>
@@ -3229,35 +3226,35 @@
         <v>9</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>114</v>
@@ -3269,15 +3266,15 @@
         <v>9</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>115</v>
@@ -3289,155 +3286,155 @@
         <v>9</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E92" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F92" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>123</v>
@@ -3449,195 +3446,195 @@
         <v>9</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F100" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>133</v>
@@ -3649,121 +3646,121 @@
         <v>9</v>
       </c>
       <c r="E103" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F103" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C105" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F105" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D107" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E107" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="F107" s="2" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>9</v>
@@ -3772,52 +3769,52 @@
         <v>10</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>142</v>
@@ -3826,458 +3823,438 @@
         <v>8</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B115" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B115" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>20</v>
+      <c r="C115" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="A116" s="2" t="s">
-        <v>145</v>
+      <c r="A116" s="3" t="s">
+        <v>144</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>147</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F116" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="F116" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="117" spans="1:6">
-      <c r="A117" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B117" s="3" t="s">
+      <c r="A117" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C117" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>22</v>
+      <c r="C117" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118" spans="1:6">
-      <c r="A118" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B118" s="2" t="s">
+      <c r="A118" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B118" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>22</v>
+      <c r="C118" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="119" spans="1:6">
-      <c r="A119" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B119" s="6" t="s">
+      <c r="A119" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B119" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C119" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E119" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>20</v>
+      <c r="C119" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>151</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="A121" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B121" s="3" t="s">
+      <c r="A121" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C121" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F121" s="3" t="s">
-        <v>27</v>
+      <c r="C121" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B122" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B122" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C122" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F122" s="2" t="s">
+      <c r="C122" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" s="3" t="s">
         <v>20</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B123" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B123" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C123" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F123" s="3" t="s">
-        <v>20</v>
+      <c r="C123" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B124" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B124" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C124" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>18</v>
+      <c r="C124" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B125" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="C125" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D125" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F125" s="3" t="s">
-        <v>18</v>
+      <c r="D125" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E126" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F126" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C127" s="2" t="s">
+      <c r="F128" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D127" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E127" s="2" t="s">
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D129" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F127" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D128" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F128" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>38</v>
+      <c r="E129" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="130" spans="1:6">
-      <c r="A130" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="B130" s="7" t="s">
+      <c r="A130" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C130" s="7" t="s">
+      <c r="C130" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F130" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="D130" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E130" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F130" s="7" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="132" spans="1:6">
-      <c r="A132" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B132" s="2" t="s">
+      <c r="A132" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B132" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C132" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E132" s="2" t="s">
+      <c r="C132" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="133" spans="1:6">
-      <c r="A133" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B133" s="3" t="s">
+      <c r="A133" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B133" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C133" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E133" s="3" t="s">
+      <c r="C133" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E133" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F133" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F134" s="3" t="s">
-        <v>42</v>
+      <c r="F133" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F134" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:F134">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F133" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:F133">
       <sortCondition ref="A2:A134" customList="传说,史诗,稀有,普通"/>
       <sortCondition ref="B2:B134"/>
     </sortState>
@@ -4286,7 +4263,7 @@
   <sortState ref="A2:F135">
     <sortCondition ref="A2:A135" customList="橙色,紫色,蓝色,绿色"/>
   </sortState>
-  <conditionalFormatting sqref="A2:F229">
+  <conditionalFormatting sqref="A2:F228">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$A2="传说"</formula>
     </cfRule>
